--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R682edc2c1686497b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R1fb24dca0b1441cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Rfec64f36464348f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R33c0210820214c55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R3c6ceb2409934af6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R41c5d89ee9b24807"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rcdc809fc1e9147ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R33aed99a469242e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R4a31710491634ead"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R64df0b8f165d47cd"/>
   </x:sheets>
 </x:workbook>
 </file>
